--- a/reports/Security_Review_Audit_Report_400.xlsx
+++ b/reports/Security_Review_Audit_Report_400.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="834">
   <si>
     <t>Finding ID</t>
   </si>
@@ -52,7 +52,7 @@
     <t>PASSED (0 Critical)</t>
   </si>
   <si>
-    <t>2026-08-07T15:22:43.166Z</t>
+    <t>2026-08-07T04:03:04.298Z</t>
   </si>
   <si>
     <t>Zero Critical / Zero High vulnerabilities detected (Overall Score: 72/100 Low Risk)</t>
@@ -88,6 +88,9 @@
     <t>Local Storage &amp; Session Protection - Security Audit Check #6: Vulnerability analysis &amp; hardening verification</t>
   </si>
   <si>
+    <t>2026-08-07T04:03:04.299Z</t>
+  </si>
+  <si>
     <t>SEC-TC-0007</t>
   </si>
   <si>
@@ -118,9 +121,6 @@
     <t>Local Storage &amp; Session Protection - Security Audit Check #11: Vulnerability analysis &amp; hardening verification</t>
   </si>
   <si>
-    <t>2026-08-07T15:22:43.167Z</t>
-  </si>
-  <si>
     <t>SEC-TC-0012</t>
   </si>
   <si>
@@ -2075,6 +2075,9 @@
   </si>
   <si>
     <t>REST API Request Schemas - Security Audit Check #9: Vulnerability analysis &amp; hardening verification</t>
+  </si>
+  <si>
+    <t>2026-08-07T04:03:04.300Z</t>
   </si>
   <si>
     <t>SEC-TC-0330</t>
@@ -3004,7 +3007,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
@@ -3030,7 +3033,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
@@ -3056,7 +3059,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>12</v>
@@ -3082,7 +3085,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>12</v>
@@ -3134,13 +3137,13 @@
         <v>11</v>
       </c>
       <c r="E7" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>14</v>
@@ -3148,13 +3151,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -3166,7 +3169,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
@@ -3174,13 +3177,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>11</v>
@@ -3192,7 +3195,7 @@
         <v>12</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
@@ -3200,25 +3203,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>14</v>
@@ -3226,13 +3229,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>11</v>
@@ -3244,7 +3247,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>14</v>
@@ -3252,25 +3255,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>14</v>
@@ -3290,13 +3293,13 @@
         <v>11</v>
       </c>
       <c r="E13" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>14</v>
@@ -3316,13 +3319,13 @@
         <v>11</v>
       </c>
       <c r="E14" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>14</v>
@@ -3342,13 +3345,13 @@
         <v>11</v>
       </c>
       <c r="E15" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>14</v>
@@ -3374,7 +3377,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>14</v>
@@ -3394,13 +3397,13 @@
         <v>11</v>
       </c>
       <c r="E17" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>14</v>
@@ -3420,13 +3423,13 @@
         <v>11</v>
       </c>
       <c r="E18" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>14</v>
@@ -3452,7 +3455,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>14</v>
@@ -3472,13 +3475,13 @@
         <v>11</v>
       </c>
       <c r="E20" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>14</v>
@@ -3498,13 +3501,13 @@
         <v>11</v>
       </c>
       <c r="E21" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>14</v>
@@ -3524,13 +3527,13 @@
         <v>11</v>
       </c>
       <c r="E22" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>14</v>
@@ -3550,13 +3553,13 @@
         <v>11</v>
       </c>
       <c r="E23" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>14</v>
@@ -3576,13 +3579,13 @@
         <v>11</v>
       </c>
       <c r="E24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>14</v>
@@ -3602,13 +3605,13 @@
         <v>11</v>
       </c>
       <c r="E25" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>14</v>
@@ -3628,13 +3631,13 @@
         <v>11</v>
       </c>
       <c r="E26" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>14</v>
@@ -3660,7 +3663,7 @@
         <v>12</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>14</v>
@@ -3686,7 +3689,7 @@
         <v>12</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>14</v>
@@ -3712,7 +3715,7 @@
         <v>12</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>14</v>
@@ -3732,13 +3735,13 @@
         <v>11</v>
       </c>
       <c r="E30" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>14</v>
@@ -3758,13 +3761,13 @@
         <v>11</v>
       </c>
       <c r="E31" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>14</v>
@@ -3784,13 +3787,13 @@
         <v>11</v>
       </c>
       <c r="E32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>14</v>
@@ -3810,13 +3813,13 @@
         <v>11</v>
       </c>
       <c r="E33" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>14</v>
@@ -3836,13 +3839,13 @@
         <v>11</v>
       </c>
       <c r="E34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>14</v>
@@ -3868,7 +3871,7 @@
         <v>12</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>14</v>
@@ -3888,13 +3891,13 @@
         <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>14</v>
@@ -3920,7 +3923,7 @@
         <v>12</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>14</v>
@@ -3940,13 +3943,13 @@
         <v>11</v>
       </c>
       <c r="E38" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>14</v>
@@ -3972,7 +3975,7 @@
         <v>12</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>14</v>
@@ -3992,13 +3995,13 @@
         <v>11</v>
       </c>
       <c r="E40" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>14</v>
@@ -4018,13 +4021,13 @@
         <v>11</v>
       </c>
       <c r="E41" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>14</v>
@@ -4044,13 +4047,13 @@
         <v>11</v>
       </c>
       <c r="E42" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>14</v>
@@ -4070,13 +4073,13 @@
         <v>11</v>
       </c>
       <c r="E43" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>14</v>
@@ -4096,13 +4099,13 @@
         <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>14</v>
@@ -4122,13 +4125,13 @@
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>14</v>
@@ -4154,7 +4157,7 @@
         <v>12</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>14</v>
@@ -4174,13 +4177,13 @@
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>14</v>
@@ -4200,13 +4203,13 @@
         <v>11</v>
       </c>
       <c r="E48" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>14</v>
@@ -4226,13 +4229,13 @@
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>14</v>
@@ -4258,7 +4261,7 @@
         <v>12</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>14</v>
@@ -4278,13 +4281,13 @@
         <v>11</v>
       </c>
       <c r="E51" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>14</v>
@@ -4304,13 +4307,13 @@
         <v>11</v>
       </c>
       <c r="E52" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>14</v>
@@ -4330,13 +4333,13 @@
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>14</v>
@@ -4356,13 +4359,13 @@
         <v>11</v>
       </c>
       <c r="E54" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>14</v>
@@ -4382,13 +4385,13 @@
         <v>11</v>
       </c>
       <c r="E55" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>14</v>
@@ -4408,13 +4411,13 @@
         <v>11</v>
       </c>
       <c r="E56" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>14</v>
@@ -4434,13 +4437,13 @@
         <v>11</v>
       </c>
       <c r="E57" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>14</v>
@@ -4460,13 +4463,13 @@
         <v>11</v>
       </c>
       <c r="E58" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>14</v>
@@ -4492,7 +4495,7 @@
         <v>12</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>14</v>
@@ -4512,13 +4515,13 @@
         <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>14</v>
@@ -4538,13 +4541,13 @@
         <v>11</v>
       </c>
       <c r="E61" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>14</v>
@@ -4570,7 +4573,7 @@
         <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>14</v>
@@ -4590,13 +4593,13 @@
         <v>11</v>
       </c>
       <c r="E63" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>14</v>
@@ -4616,13 +4619,13 @@
         <v>11</v>
       </c>
       <c r="E64" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>14</v>
@@ -4642,13 +4645,13 @@
         <v>11</v>
       </c>
       <c r="E65" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>14</v>
@@ -4668,13 +4671,13 @@
         <v>11</v>
       </c>
       <c r="E66" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>14</v>
@@ -4700,7 +4703,7 @@
         <v>12</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>14</v>
@@ -4720,13 +4723,13 @@
         <v>11</v>
       </c>
       <c r="E68" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>14</v>
@@ -4752,7 +4755,7 @@
         <v>12</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>14</v>
@@ -4772,13 +4775,13 @@
         <v>11</v>
       </c>
       <c r="E70" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>14</v>
@@ -4798,13 +4801,13 @@
         <v>11</v>
       </c>
       <c r="E71" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>14</v>
@@ -4830,7 +4833,7 @@
         <v>12</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>14</v>
@@ -4850,13 +4853,13 @@
         <v>11</v>
       </c>
       <c r="E73" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>14</v>
@@ -4876,13 +4879,13 @@
         <v>11</v>
       </c>
       <c r="E74" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>14</v>
@@ -4902,13 +4905,13 @@
         <v>11</v>
       </c>
       <c r="E75" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>14</v>
@@ -4928,13 +4931,13 @@
         <v>11</v>
       </c>
       <c r="E76" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>14</v>
@@ -4954,13 +4957,13 @@
         <v>11</v>
       </c>
       <c r="E77" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>14</v>
@@ -4980,13 +4983,13 @@
         <v>11</v>
       </c>
       <c r="E78" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>14</v>
@@ -5006,13 +5009,13 @@
         <v>11</v>
       </c>
       <c r="E79" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>14</v>
@@ -5038,7 +5041,7 @@
         <v>12</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>14</v>
@@ -5058,13 +5061,13 @@
         <v>11</v>
       </c>
       <c r="E81" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>14</v>
@@ -5084,13 +5087,13 @@
         <v>11</v>
       </c>
       <c r="E82" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>14</v>
@@ -5116,7 +5119,7 @@
         <v>12</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>14</v>
@@ -5136,13 +5139,13 @@
         <v>11</v>
       </c>
       <c r="E84" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>14</v>
@@ -5162,13 +5165,13 @@
         <v>11</v>
       </c>
       <c r="E85" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>14</v>
@@ -5188,13 +5191,13 @@
         <v>11</v>
       </c>
       <c r="E86" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>14</v>
@@ -5214,13 +5217,13 @@
         <v>11</v>
       </c>
       <c r="E87" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>14</v>
@@ -5240,13 +5243,13 @@
         <v>11</v>
       </c>
       <c r="E88" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>14</v>
@@ -5266,13 +5269,13 @@
         <v>11</v>
       </c>
       <c r="E89" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>14</v>
@@ -5298,7 +5301,7 @@
         <v>12</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>14</v>
@@ -5318,13 +5321,13 @@
         <v>11</v>
       </c>
       <c r="E91" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>14</v>
@@ -5344,13 +5347,13 @@
         <v>11</v>
       </c>
       <c r="E92" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>14</v>
@@ -5370,13 +5373,13 @@
         <v>11</v>
       </c>
       <c r="E93" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>14</v>
@@ -5402,7 +5405,7 @@
         <v>12</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>14</v>
@@ -5428,7 +5431,7 @@
         <v>12</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>14</v>
@@ -5448,13 +5451,13 @@
         <v>11</v>
       </c>
       <c r="E96" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>14</v>
@@ -5474,13 +5477,13 @@
         <v>11</v>
       </c>
       <c r="E97" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>14</v>
@@ -5500,13 +5503,13 @@
         <v>11</v>
       </c>
       <c r="E98" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>14</v>
@@ -5526,13 +5529,13 @@
         <v>11</v>
       </c>
       <c r="E99" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>14</v>
@@ -5552,13 +5555,13 @@
         <v>11</v>
       </c>
       <c r="E100" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>14</v>
@@ -5578,13 +5581,13 @@
         <v>11</v>
       </c>
       <c r="E101" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>14</v>
@@ -5604,13 +5607,13 @@
         <v>11</v>
       </c>
       <c r="E102" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>14</v>
@@ -5630,13 +5633,13 @@
         <v>11</v>
       </c>
       <c r="E103" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>14</v>
@@ -5656,13 +5659,13 @@
         <v>11</v>
       </c>
       <c r="E104" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>14</v>
@@ -5682,13 +5685,13 @@
         <v>11</v>
       </c>
       <c r="E105" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>14</v>
@@ -5708,13 +5711,13 @@
         <v>11</v>
       </c>
       <c r="E106" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>14</v>
@@ -5734,13 +5737,13 @@
         <v>11</v>
       </c>
       <c r="E107" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>14</v>
@@ -5766,7 +5769,7 @@
         <v>12</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>14</v>
@@ -5786,13 +5789,13 @@
         <v>11</v>
       </c>
       <c r="E109" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>14</v>
@@ -5818,7 +5821,7 @@
         <v>12</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>14</v>
@@ -5844,7 +5847,7 @@
         <v>12</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>14</v>
@@ -5864,13 +5867,13 @@
         <v>11</v>
       </c>
       <c r="E112" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>14</v>
@@ -5896,7 +5899,7 @@
         <v>12</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>14</v>
@@ -5916,13 +5919,13 @@
         <v>11</v>
       </c>
       <c r="E114" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>14</v>
@@ -5942,13 +5945,13 @@
         <v>11</v>
       </c>
       <c r="E115" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>14</v>
@@ -5968,13 +5971,13 @@
         <v>11</v>
       </c>
       <c r="E116" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>14</v>
@@ -5994,13 +5997,13 @@
         <v>11</v>
       </c>
       <c r="E117" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>14</v>
@@ -6020,13 +6023,13 @@
         <v>11</v>
       </c>
       <c r="E118" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>14</v>
@@ -6052,7 +6055,7 @@
         <v>12</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>14</v>
@@ -6072,13 +6075,13 @@
         <v>11</v>
       </c>
       <c r="E120" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>14</v>
@@ -6098,13 +6101,13 @@
         <v>11</v>
       </c>
       <c r="E121" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>14</v>
@@ -6124,13 +6127,13 @@
         <v>11</v>
       </c>
       <c r="E122" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>14</v>
@@ -6156,7 +6159,7 @@
         <v>12</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>14</v>
@@ -6176,13 +6179,13 @@
         <v>11</v>
       </c>
       <c r="E124" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>14</v>
@@ -6202,13 +6205,13 @@
         <v>11</v>
       </c>
       <c r="E125" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>14</v>
@@ -6228,13 +6231,13 @@
         <v>11</v>
       </c>
       <c r="E126" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>14</v>
@@ -6254,13 +6257,13 @@
         <v>11</v>
       </c>
       <c r="E127" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>14</v>
@@ -6286,7 +6289,7 @@
         <v>12</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>14</v>
@@ -6306,13 +6309,13 @@
         <v>11</v>
       </c>
       <c r="E129" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>14</v>
@@ -6332,13 +6335,13 @@
         <v>11</v>
       </c>
       <c r="E130" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>14</v>
@@ -6364,7 +6367,7 @@
         <v>12</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>14</v>
@@ -6384,13 +6387,13 @@
         <v>11</v>
       </c>
       <c r="E132" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>14</v>
@@ -6416,7 +6419,7 @@
         <v>12</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>14</v>
@@ -6436,13 +6439,13 @@
         <v>11</v>
       </c>
       <c r="E134" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>14</v>
@@ -6462,13 +6465,13 @@
         <v>11</v>
       </c>
       <c r="E135" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>14</v>
@@ -6494,7 +6497,7 @@
         <v>12</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>14</v>
@@ -6514,13 +6517,13 @@
         <v>11</v>
       </c>
       <c r="E137" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>14</v>
@@ -6540,13 +6543,13 @@
         <v>11</v>
       </c>
       <c r="E138" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>14</v>
@@ -6566,13 +6569,13 @@
         <v>11</v>
       </c>
       <c r="E139" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>14</v>
@@ -6592,13 +6595,13 @@
         <v>11</v>
       </c>
       <c r="E140" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>14</v>
@@ -6618,13 +6621,13 @@
         <v>11</v>
       </c>
       <c r="E141" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>14</v>
@@ -6644,13 +6647,13 @@
         <v>11</v>
       </c>
       <c r="E142" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>14</v>
@@ -6676,7 +6679,7 @@
         <v>12</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>14</v>
@@ -6696,13 +6699,13 @@
         <v>11</v>
       </c>
       <c r="E144" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>14</v>
@@ -6722,13 +6725,13 @@
         <v>11</v>
       </c>
       <c r="E145" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>14</v>
@@ -6748,13 +6751,13 @@
         <v>11</v>
       </c>
       <c r="E146" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>14</v>
@@ -6774,13 +6777,13 @@
         <v>11</v>
       </c>
       <c r="E147" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>14</v>
@@ -6800,13 +6803,13 @@
         <v>11</v>
       </c>
       <c r="E148" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>14</v>
@@ -6826,13 +6829,13 @@
         <v>11</v>
       </c>
       <c r="E149" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>14</v>
@@ -6852,13 +6855,13 @@
         <v>11</v>
       </c>
       <c r="E150" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>14</v>
@@ -6878,13 +6881,13 @@
         <v>11</v>
       </c>
       <c r="E151" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H151" s="4" t="s">
         <v>14</v>
@@ -6904,13 +6907,13 @@
         <v>11</v>
       </c>
       <c r="E152" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>14</v>
@@ -6930,13 +6933,13 @@
         <v>11</v>
       </c>
       <c r="E153" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>14</v>
@@ -6962,7 +6965,7 @@
         <v>12</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>14</v>
@@ -6982,13 +6985,13 @@
         <v>11</v>
       </c>
       <c r="E155" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>14</v>
@@ -7008,13 +7011,13 @@
         <v>11</v>
       </c>
       <c r="E156" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>14</v>
@@ -7034,13 +7037,13 @@
         <v>11</v>
       </c>
       <c r="E157" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>14</v>
@@ -7060,13 +7063,13 @@
         <v>11</v>
       </c>
       <c r="E158" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>14</v>
@@ -7086,13 +7089,13 @@
         <v>11</v>
       </c>
       <c r="E159" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>14</v>
@@ -7118,7 +7121,7 @@
         <v>12</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>14</v>
@@ -7138,13 +7141,13 @@
         <v>11</v>
       </c>
       <c r="E161" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>14</v>
@@ -7170,7 +7173,7 @@
         <v>12</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>14</v>
@@ -7190,13 +7193,13 @@
         <v>11</v>
       </c>
       <c r="E163" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>14</v>
@@ -7216,13 +7219,13 @@
         <v>11</v>
       </c>
       <c r="E164" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>14</v>
@@ -7242,13 +7245,13 @@
         <v>11</v>
       </c>
       <c r="E165" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>14</v>
@@ -7268,13 +7271,13 @@
         <v>11</v>
       </c>
       <c r="E166" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>14</v>
@@ -7294,13 +7297,13 @@
         <v>11</v>
       </c>
       <c r="E167" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>14</v>
@@ -7326,7 +7329,7 @@
         <v>12</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>14</v>
@@ -7352,7 +7355,7 @@
         <v>12</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>14</v>
@@ -7372,13 +7375,13 @@
         <v>11</v>
       </c>
       <c r="E170" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>14</v>
@@ -7398,13 +7401,13 @@
         <v>11</v>
       </c>
       <c r="E171" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H171" s="4" t="s">
         <v>14</v>
@@ -7424,13 +7427,13 @@
         <v>11</v>
       </c>
       <c r="E172" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>14</v>
@@ -7450,13 +7453,13 @@
         <v>11</v>
       </c>
       <c r="E173" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>14</v>
@@ -7476,13 +7479,13 @@
         <v>11</v>
       </c>
       <c r="E174" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>14</v>
@@ -7502,13 +7505,13 @@
         <v>11</v>
       </c>
       <c r="E175" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>14</v>
@@ -7528,13 +7531,13 @@
         <v>11</v>
       </c>
       <c r="E176" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>14</v>
@@ -7560,7 +7563,7 @@
         <v>12</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>14</v>
@@ -7580,13 +7583,13 @@
         <v>11</v>
       </c>
       <c r="E178" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>14</v>
@@ -7606,13 +7609,13 @@
         <v>11</v>
       </c>
       <c r="E179" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>14</v>
@@ -7638,7 +7641,7 @@
         <v>12</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>14</v>
@@ -7658,13 +7661,13 @@
         <v>11</v>
       </c>
       <c r="E181" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>14</v>
@@ -7684,13 +7687,13 @@
         <v>11</v>
       </c>
       <c r="E182" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>14</v>
@@ -7710,13 +7713,13 @@
         <v>11</v>
       </c>
       <c r="E183" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>14</v>
@@ -7742,7 +7745,7 @@
         <v>12</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>14</v>
@@ -7762,13 +7765,13 @@
         <v>11</v>
       </c>
       <c r="E185" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>14</v>
@@ -7788,13 +7791,13 @@
         <v>11</v>
       </c>
       <c r="E186" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>14</v>
@@ -7814,13 +7817,13 @@
         <v>11</v>
       </c>
       <c r="E187" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>14</v>
@@ -7840,13 +7843,13 @@
         <v>11</v>
       </c>
       <c r="E188" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>14</v>
@@ -7866,13 +7869,13 @@
         <v>11</v>
       </c>
       <c r="E189" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>14</v>
@@ -7892,13 +7895,13 @@
         <v>11</v>
       </c>
       <c r="E190" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>14</v>
@@ -7918,13 +7921,13 @@
         <v>11</v>
       </c>
       <c r="E191" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>14</v>
@@ -7944,13 +7947,13 @@
         <v>11</v>
       </c>
       <c r="E192" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>14</v>
@@ -7970,13 +7973,13 @@
         <v>11</v>
       </c>
       <c r="E193" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>14</v>
@@ -7996,13 +7999,13 @@
         <v>11</v>
       </c>
       <c r="E194" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>14</v>
@@ -8022,13 +8025,13 @@
         <v>11</v>
       </c>
       <c r="E195" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>14</v>
@@ -8048,13 +8051,13 @@
         <v>11</v>
       </c>
       <c r="E196" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>14</v>
@@ -8074,13 +8077,13 @@
         <v>11</v>
       </c>
       <c r="E197" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>14</v>
@@ -8100,13 +8103,13 @@
         <v>11</v>
       </c>
       <c r="E198" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>14</v>
@@ -8126,13 +8129,13 @@
         <v>11</v>
       </c>
       <c r="E199" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H199" s="4" t="s">
         <v>14</v>
@@ -8152,13 +8155,13 @@
         <v>11</v>
       </c>
       <c r="E200" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>14</v>
@@ -8178,13 +8181,13 @@
         <v>11</v>
       </c>
       <c r="E201" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>14</v>
@@ -8204,13 +8207,13 @@
         <v>11</v>
       </c>
       <c r="E202" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>14</v>
@@ -8230,13 +8233,13 @@
         <v>11</v>
       </c>
       <c r="E203" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>14</v>
@@ -8256,13 +8259,13 @@
         <v>11</v>
       </c>
       <c r="E204" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>14</v>
@@ -8282,13 +8285,13 @@
         <v>11</v>
       </c>
       <c r="E205" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H205" s="4" t="s">
         <v>14</v>
@@ -8314,7 +8317,7 @@
         <v>12</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>14</v>
@@ -8334,13 +8337,13 @@
         <v>11</v>
       </c>
       <c r="E207" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H207" s="4" t="s">
         <v>14</v>
@@ -8360,13 +8363,13 @@
         <v>11</v>
       </c>
       <c r="E208" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>14</v>
@@ -8386,13 +8389,13 @@
         <v>11</v>
       </c>
       <c r="E209" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>14</v>
@@ -8418,7 +8421,7 @@
         <v>12</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>14</v>
@@ -8444,7 +8447,7 @@
         <v>12</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H211" s="4" t="s">
         <v>14</v>
@@ -8464,13 +8467,13 @@
         <v>11</v>
       </c>
       <c r="E212" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>14</v>
@@ -8490,13 +8493,13 @@
         <v>11</v>
       </c>
       <c r="E213" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>14</v>
@@ -8516,13 +8519,13 @@
         <v>11</v>
       </c>
       <c r="E214" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>14</v>
@@ -8542,13 +8545,13 @@
         <v>11</v>
       </c>
       <c r="E215" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>14</v>
@@ -8568,13 +8571,13 @@
         <v>11</v>
       </c>
       <c r="E216" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>14</v>
@@ -8600,7 +8603,7 @@
         <v>12</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H217" s="4" t="s">
         <v>14</v>
@@ -8620,13 +8623,13 @@
         <v>11</v>
       </c>
       <c r="E218" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>14</v>
@@ -8646,13 +8649,13 @@
         <v>11</v>
       </c>
       <c r="E219" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>14</v>
@@ -8672,13 +8675,13 @@
         <v>11</v>
       </c>
       <c r="E220" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>14</v>
@@ -8698,13 +8701,13 @@
         <v>11</v>
       </c>
       <c r="E221" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>14</v>
@@ -8730,7 +8733,7 @@
         <v>12</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>14</v>
@@ -8750,13 +8753,13 @@
         <v>11</v>
       </c>
       <c r="E223" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>14</v>
@@ -8776,13 +8779,13 @@
         <v>11</v>
       </c>
       <c r="E224" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>14</v>
@@ -8802,13 +8805,13 @@
         <v>11</v>
       </c>
       <c r="E225" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>14</v>
@@ -8828,13 +8831,13 @@
         <v>11</v>
       </c>
       <c r="E226" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>14</v>
@@ -8854,13 +8857,13 @@
         <v>11</v>
       </c>
       <c r="E227" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>14</v>
@@ -8880,13 +8883,13 @@
         <v>11</v>
       </c>
       <c r="E228" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>14</v>
@@ -8906,13 +8909,13 @@
         <v>11</v>
       </c>
       <c r="E229" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>14</v>
@@ -8932,13 +8935,13 @@
         <v>11</v>
       </c>
       <c r="E230" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>14</v>
@@ -8958,13 +8961,13 @@
         <v>11</v>
       </c>
       <c r="E231" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>14</v>
@@ -8984,13 +8987,13 @@
         <v>11</v>
       </c>
       <c r="E232" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>14</v>
@@ -9010,13 +9013,13 @@
         <v>11</v>
       </c>
       <c r="E233" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>14</v>
@@ -9036,13 +9039,13 @@
         <v>11</v>
       </c>
       <c r="E234" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>14</v>
@@ -9062,13 +9065,13 @@
         <v>11</v>
       </c>
       <c r="E235" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>14</v>
@@ -9088,13 +9091,13 @@
         <v>11</v>
       </c>
       <c r="E236" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>14</v>
@@ -9114,13 +9117,13 @@
         <v>11</v>
       </c>
       <c r="E237" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>14</v>
@@ -9140,13 +9143,13 @@
         <v>11</v>
       </c>
       <c r="E238" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>14</v>
@@ -9166,13 +9169,13 @@
         <v>11</v>
       </c>
       <c r="E239" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>14</v>
@@ -9192,13 +9195,13 @@
         <v>11</v>
       </c>
       <c r="E240" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>14</v>
@@ -9224,7 +9227,7 @@
         <v>12</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H241" s="4" t="s">
         <v>14</v>
@@ -9244,13 +9247,13 @@
         <v>11</v>
       </c>
       <c r="E242" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>14</v>
@@ -9270,13 +9273,13 @@
         <v>11</v>
       </c>
       <c r="E243" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>14</v>
@@ -9296,13 +9299,13 @@
         <v>11</v>
       </c>
       <c r="E244" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>14</v>
@@ -9322,13 +9325,13 @@
         <v>11</v>
       </c>
       <c r="E245" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>14</v>
@@ -9348,13 +9351,13 @@
         <v>11</v>
       </c>
       <c r="E246" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>14</v>
@@ -9380,7 +9383,7 @@
         <v>12</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>14</v>
@@ -9400,13 +9403,13 @@
         <v>11</v>
       </c>
       <c r="E248" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>14</v>
@@ -9426,13 +9429,13 @@
         <v>11</v>
       </c>
       <c r="E249" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>14</v>
@@ -9458,7 +9461,7 @@
         <v>12</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>14</v>
@@ -9478,13 +9481,13 @@
         <v>11</v>
       </c>
       <c r="E251" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>14</v>
@@ -9504,13 +9507,13 @@
         <v>11</v>
       </c>
       <c r="E252" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>14</v>
@@ -9536,7 +9539,7 @@
         <v>12</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H253" s="4" t="s">
         <v>14</v>
@@ -9556,13 +9559,13 @@
         <v>11</v>
       </c>
       <c r="E254" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>14</v>
@@ -9582,13 +9585,13 @@
         <v>11</v>
       </c>
       <c r="E255" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>14</v>
@@ -9608,13 +9611,13 @@
         <v>11</v>
       </c>
       <c r="E256" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>14</v>
@@ -9634,13 +9637,13 @@
         <v>11</v>
       </c>
       <c r="E257" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H257" s="4" t="s">
         <v>14</v>
@@ -9660,13 +9663,13 @@
         <v>11</v>
       </c>
       <c r="E258" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>14</v>
@@ -9686,13 +9689,13 @@
         <v>11</v>
       </c>
       <c r="E259" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H259" s="4" t="s">
         <v>14</v>
@@ -9712,13 +9715,13 @@
         <v>11</v>
       </c>
       <c r="E260" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>14</v>
@@ -9738,13 +9741,13 @@
         <v>11</v>
       </c>
       <c r="E261" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H261" s="4" t="s">
         <v>14</v>
@@ -9764,13 +9767,13 @@
         <v>11</v>
       </c>
       <c r="E262" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>14</v>
@@ -9796,7 +9799,7 @@
         <v>12</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H263" s="4" t="s">
         <v>14</v>
@@ -9816,13 +9819,13 @@
         <v>11</v>
       </c>
       <c r="E264" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>14</v>
@@ -9842,13 +9845,13 @@
         <v>11</v>
       </c>
       <c r="E265" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H265" s="4" t="s">
         <v>14</v>
@@ -9868,13 +9871,13 @@
         <v>11</v>
       </c>
       <c r="E266" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>14</v>
@@ -9900,7 +9903,7 @@
         <v>12</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H267" s="4" t="s">
         <v>14</v>
@@ -9926,7 +9929,7 @@
         <v>12</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>14</v>
@@ -9946,13 +9949,13 @@
         <v>11</v>
       </c>
       <c r="E269" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H269" s="4" t="s">
         <v>14</v>
@@ -9972,13 +9975,13 @@
         <v>11</v>
       </c>
       <c r="E270" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>14</v>
@@ -9998,13 +10001,13 @@
         <v>11</v>
       </c>
       <c r="E271" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H271" s="4" t="s">
         <v>14</v>
@@ -10030,7 +10033,7 @@
         <v>12</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>14</v>
@@ -10050,13 +10053,13 @@
         <v>11</v>
       </c>
       <c r="E273" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H273" s="4" t="s">
         <v>14</v>
@@ -10076,13 +10079,13 @@
         <v>11</v>
       </c>
       <c r="E274" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>14</v>
@@ -10102,13 +10105,13 @@
         <v>11</v>
       </c>
       <c r="E275" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G275" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H275" s="4" t="s">
         <v>14</v>
@@ -10134,7 +10137,7 @@
         <v>12</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>14</v>
@@ -10160,7 +10163,7 @@
         <v>12</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H277" s="4" t="s">
         <v>14</v>
@@ -10180,13 +10183,13 @@
         <v>11</v>
       </c>
       <c r="E278" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>14</v>
@@ -10206,13 +10209,13 @@
         <v>11</v>
       </c>
       <c r="E279" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H279" s="4" t="s">
         <v>14</v>
@@ -10232,13 +10235,13 @@
         <v>11</v>
       </c>
       <c r="E280" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>14</v>
@@ -10264,7 +10267,7 @@
         <v>12</v>
       </c>
       <c r="G281" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H281" s="4" t="s">
         <v>14</v>
@@ -10284,13 +10287,13 @@
         <v>11</v>
       </c>
       <c r="E282" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>14</v>
@@ -10310,13 +10313,13 @@
         <v>11</v>
       </c>
       <c r="E283" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H283" s="4" t="s">
         <v>14</v>
@@ -10336,13 +10339,13 @@
         <v>11</v>
       </c>
       <c r="E284" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>14</v>
@@ -10362,13 +10365,13 @@
         <v>11</v>
       </c>
       <c r="E285" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G285" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H285" s="4" t="s">
         <v>14</v>
@@ -10388,13 +10391,13 @@
         <v>11</v>
       </c>
       <c r="E286" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>14</v>
@@ -10414,13 +10417,13 @@
         <v>11</v>
       </c>
       <c r="E287" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H287" s="4" t="s">
         <v>14</v>
@@ -10446,7 +10449,7 @@
         <v>12</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>14</v>
@@ -10466,13 +10469,13 @@
         <v>11</v>
       </c>
       <c r="E289" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G289" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H289" s="4" t="s">
         <v>14</v>
@@ -10492,13 +10495,13 @@
         <v>11</v>
       </c>
       <c r="E290" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>14</v>
@@ -10524,7 +10527,7 @@
         <v>12</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H291" s="4" t="s">
         <v>14</v>
@@ -10544,13 +10547,13 @@
         <v>11</v>
       </c>
       <c r="E292" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>14</v>
@@ -10570,13 +10573,13 @@
         <v>11</v>
       </c>
       <c r="E293" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H293" s="4" t="s">
         <v>14</v>
@@ -10596,13 +10599,13 @@
         <v>11</v>
       </c>
       <c r="E294" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>14</v>
@@ -10622,13 +10625,13 @@
         <v>11</v>
       </c>
       <c r="E295" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H295" s="4" t="s">
         <v>14</v>
@@ -10648,13 +10651,13 @@
         <v>11</v>
       </c>
       <c r="E296" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>14</v>
@@ -10674,13 +10677,13 @@
         <v>11</v>
       </c>
       <c r="E297" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H297" s="4" t="s">
         <v>14</v>
@@ -10706,7 +10709,7 @@
         <v>12</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>14</v>
@@ -10726,13 +10729,13 @@
         <v>11</v>
       </c>
       <c r="E299" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H299" s="4" t="s">
         <v>14</v>
@@ -10752,13 +10755,13 @@
         <v>11</v>
       </c>
       <c r="E300" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>14</v>
@@ -10784,7 +10787,7 @@
         <v>12</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H301" s="4" t="s">
         <v>14</v>
@@ -10804,13 +10807,13 @@
         <v>11</v>
       </c>
       <c r="E302" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>14</v>
@@ -10830,13 +10833,13 @@
         <v>11</v>
       </c>
       <c r="E303" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H303" s="4" t="s">
         <v>14</v>
@@ -10862,7 +10865,7 @@
         <v>12</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>14</v>
@@ -10882,13 +10885,13 @@
         <v>11</v>
       </c>
       <c r="E305" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>14</v>
@@ -10908,13 +10911,13 @@
         <v>11</v>
       </c>
       <c r="E306" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>14</v>
@@ -10940,7 +10943,7 @@
         <v>12</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>14</v>
@@ -10960,13 +10963,13 @@
         <v>11</v>
       </c>
       <c r="E308" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>14</v>
@@ -10986,13 +10989,13 @@
         <v>11</v>
       </c>
       <c r="E309" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H309" s="4" t="s">
         <v>14</v>
@@ -11012,13 +11015,13 @@
         <v>11</v>
       </c>
       <c r="E310" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>14</v>
@@ -11038,13 +11041,13 @@
         <v>11</v>
       </c>
       <c r="E311" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H311" s="4" t="s">
         <v>14</v>
@@ -11064,13 +11067,13 @@
         <v>11</v>
       </c>
       <c r="E312" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>14</v>
@@ -11096,7 +11099,7 @@
         <v>12</v>
       </c>
       <c r="G313" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H313" s="4" t="s">
         <v>14</v>
@@ -11116,13 +11119,13 @@
         <v>11</v>
       </c>
       <c r="E314" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>14</v>
@@ -11148,7 +11151,7 @@
         <v>12</v>
       </c>
       <c r="G315" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H315" s="4" t="s">
         <v>14</v>
@@ -11168,13 +11171,13 @@
         <v>11</v>
       </c>
       <c r="E316" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>14</v>
@@ -11200,7 +11203,7 @@
         <v>12</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H317" s="4" t="s">
         <v>14</v>
@@ -11226,7 +11229,7 @@
         <v>12</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>14</v>
@@ -11246,13 +11249,13 @@
         <v>11</v>
       </c>
       <c r="E319" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H319" s="4" t="s">
         <v>14</v>
@@ -11272,13 +11275,13 @@
         <v>11</v>
       </c>
       <c r="E320" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>14</v>
@@ -11298,13 +11301,13 @@
         <v>11</v>
       </c>
       <c r="E321" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H321" s="4" t="s">
         <v>14</v>
@@ -11324,13 +11327,13 @@
         <v>11</v>
       </c>
       <c r="E322" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>14</v>
@@ -11356,7 +11359,7 @@
         <v>12</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H323" s="4" t="s">
         <v>14</v>
@@ -11376,13 +11379,13 @@
         <v>11</v>
       </c>
       <c r="E324" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>14</v>
@@ -11402,13 +11405,13 @@
         <v>11</v>
       </c>
       <c r="E325" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H325" s="4" t="s">
         <v>14</v>
@@ -11428,13 +11431,13 @@
         <v>11</v>
       </c>
       <c r="E326" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>14</v>
@@ -11460,7 +11463,7 @@
         <v>12</v>
       </c>
       <c r="G327" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H327" s="4" t="s">
         <v>14</v>
@@ -11480,13 +11483,13 @@
         <v>11</v>
       </c>
       <c r="E328" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>14</v>
@@ -11506,13 +11509,13 @@
         <v>11</v>
       </c>
       <c r="E329" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H329" s="4" t="s">
         <v>14</v>
@@ -11532,13 +11535,13 @@
         <v>11</v>
       </c>
       <c r="E330" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>14</v>
@@ -11546,25 +11549,25 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B331" s="4" t="s">
         <v>670</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E331" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H331" s="4" t="s">
         <v>14</v>
@@ -11572,25 +11575,25 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>670</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E332" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>14</v>
@@ -11598,25 +11601,25 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B333" s="4" t="s">
         <v>670</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E333" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>14</v>
@@ -11624,13 +11627,13 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>670</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>11</v>
@@ -11642,7 +11645,7 @@
         <v>12</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>14</v>
@@ -11650,25 +11653,25 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B335" s="4" t="s">
         <v>670</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E335" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>14</v>
@@ -11676,25 +11679,25 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>670</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E336" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>14</v>
@@ -11702,13 +11705,13 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B337" s="4" t="s">
         <v>670</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>11</v>
@@ -11720,7 +11723,7 @@
         <v>12</v>
       </c>
       <c r="G337" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H337" s="4" t="s">
         <v>14</v>
@@ -11728,25 +11731,25 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>670</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E338" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>14</v>
@@ -11754,25 +11757,25 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B339" s="4" t="s">
         <v>670</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E339" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>14</v>
@@ -11780,13 +11783,13 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>670</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>11</v>
@@ -11798,7 +11801,7 @@
         <v>12</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H340" s="2" t="s">
         <v>14</v>
@@ -11806,25 +11809,25 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B341" s="4" t="s">
         <v>670</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E341" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G341" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H341" s="4" t="s">
         <v>14</v>
@@ -11832,25 +11835,25 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E342" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H342" s="2" t="s">
         <v>14</v>
@@ -11858,25 +11861,25 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E343" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G343" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H343" s="4" t="s">
         <v>14</v>
@@ -11884,25 +11887,25 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E344" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H344" s="2" t="s">
         <v>14</v>
@@ -11910,25 +11913,25 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E345" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G345" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H345" s="4" t="s">
         <v>14</v>
@@ -11936,25 +11939,25 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E346" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H346" s="2" t="s">
         <v>14</v>
@@ -11962,25 +11965,25 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E347" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>14</v>
@@ -11988,25 +11991,25 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E348" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H348" s="2" t="s">
         <v>14</v>
@@ -12014,25 +12017,25 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E349" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>14</v>
@@ -12040,25 +12043,25 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D350" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E350" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H350" s="2" t="s">
         <v>14</v>
@@ -12066,13 +12069,13 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>11</v>
@@ -12084,7 +12087,7 @@
         <v>12</v>
       </c>
       <c r="G351" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>14</v>
@@ -12092,13 +12095,13 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D352" s="2" t="s">
         <v>11</v>
@@ -12110,7 +12113,7 @@
         <v>12</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H352" s="2" t="s">
         <v>14</v>
@@ -12118,25 +12121,25 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E353" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>14</v>
@@ -12144,13 +12147,13 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D354" s="2" t="s">
         <v>11</v>
@@ -12162,7 +12165,7 @@
         <v>12</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H354" s="2" t="s">
         <v>14</v>
@@ -12170,25 +12173,25 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E355" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H355" s="4" t="s">
         <v>14</v>
@@ -12196,25 +12199,25 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E356" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H356" s="2" t="s">
         <v>14</v>
@@ -12222,25 +12225,25 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E357" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G357" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>14</v>
@@ -12248,13 +12251,13 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>11</v>
@@ -12266,7 +12269,7 @@
         <v>12</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H358" s="2" t="s">
         <v>14</v>
@@ -12274,25 +12277,25 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E359" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G359" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>14</v>
@@ -12300,25 +12303,25 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E360" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H360" s="2" t="s">
         <v>14</v>
@@ -12326,13 +12329,13 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>11</v>
@@ -12344,7 +12347,7 @@
         <v>12</v>
       </c>
       <c r="G361" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H361" s="4" t="s">
         <v>14</v>
@@ -12352,25 +12355,25 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E362" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H362" s="2" t="s">
         <v>14</v>
@@ -12378,25 +12381,25 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E363" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G363" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H363" s="4" t="s">
         <v>14</v>
@@ -12404,25 +12407,25 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E364" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H364" s="2" t="s">
         <v>14</v>
@@ -12430,25 +12433,25 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E365" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>14</v>
@@ -12456,25 +12459,25 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E366" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H366" s="2" t="s">
         <v>14</v>
@@ -12482,25 +12485,25 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E367" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H367" s="4" t="s">
         <v>14</v>
@@ -12508,25 +12511,25 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D368" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E368" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H368" s="2" t="s">
         <v>14</v>
@@ -12534,25 +12537,25 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E369" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>14</v>
@@ -12560,25 +12563,25 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E370" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H370" s="2" t="s">
         <v>14</v>
@@ -12586,25 +12589,25 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E371" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>14</v>
@@ -12612,25 +12615,25 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E372" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H372" s="2" t="s">
         <v>14</v>
@@ -12638,25 +12641,25 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E373" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H373" s="4" t="s">
         <v>14</v>
@@ -12664,25 +12667,25 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E374" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H374" s="2" t="s">
         <v>14</v>
@@ -12690,25 +12693,25 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E375" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H375" s="4" t="s">
         <v>14</v>
@@ -12716,25 +12719,25 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E376" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H376" s="2" t="s">
         <v>14</v>
@@ -12742,13 +12745,13 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>11</v>
@@ -12760,7 +12763,7 @@
         <v>12</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H377" s="4" t="s">
         <v>14</v>
@@ -12768,25 +12771,25 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E378" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H378" s="2" t="s">
         <v>14</v>
@@ -12794,25 +12797,25 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E379" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H379" s="4" t="s">
         <v>14</v>
@@ -12820,25 +12823,25 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D380" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E380" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H380" s="2" t="s">
         <v>14</v>
@@ -12846,13 +12849,13 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>11</v>
@@ -12864,7 +12867,7 @@
         <v>12</v>
       </c>
       <c r="G381" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H381" s="4" t="s">
         <v>14</v>
@@ -12872,25 +12875,25 @@
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E382" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H382" s="2" t="s">
         <v>14</v>
@@ -12898,25 +12901,25 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E383" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>14</v>
@@ -12924,25 +12927,25 @@
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D384" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E384" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H384" s="2" t="s">
         <v>14</v>
@@ -12950,25 +12953,25 @@
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E385" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G385" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H385" s="4" t="s">
         <v>14</v>
@@ -12976,25 +12979,25 @@
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D386" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E386" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H386" s="2" t="s">
         <v>14</v>
@@ -13002,25 +13005,25 @@
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E387" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G387" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>14</v>
@@ -13028,25 +13031,25 @@
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D388" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E388" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H388" s="2" t="s">
         <v>14</v>
@@ -13054,25 +13057,25 @@
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E389" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H389" s="4" t="s">
         <v>14</v>
@@ -13080,25 +13083,25 @@
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D390" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E390" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H390" s="2" t="s">
         <v>14</v>
@@ -13106,25 +13109,25 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E391" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H391" s="4" t="s">
         <v>14</v>
@@ -13132,25 +13135,25 @@
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D392" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E392" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H392" s="2" t="s">
         <v>14</v>
@@ -13158,25 +13161,25 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E393" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H393" s="4" t="s">
         <v>14</v>
@@ -13184,25 +13187,25 @@
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D394" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E394" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H394" s="2" t="s">
         <v>14</v>
@@ -13210,25 +13213,25 @@
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E395" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H395" s="4" t="s">
         <v>14</v>
@@ -13236,25 +13239,25 @@
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D396" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E396" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H396" s="2" t="s">
         <v>14</v>
@@ -13262,25 +13265,25 @@
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E397" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G397" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H397" s="4" t="s">
         <v>14</v>
@@ -13288,25 +13291,25 @@
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E398" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H398" s="2" t="s">
         <v>14</v>
@@ -13314,25 +13317,25 @@
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E399" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H399" s="4" t="s">
         <v>14</v>
@@ -13340,25 +13343,25 @@
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D400" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E400" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H400" s="2" t="s">
         <v>14</v>
@@ -13366,25 +13369,25 @@
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E401" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G401" s="4" t="s">
-        <v>35</v>
+        <v>688</v>
       </c>
       <c r="H401" s="4" t="s">
         <v>14</v>

--- a/reports/Security_Review_Audit_Report_400.xlsx
+++ b/reports/Security_Review_Audit_Report_400.xlsx
@@ -52,7 +52,7 @@
     <t>PASSED (0 Critical)</t>
   </si>
   <si>
-    <t>2026-08-10T08:42:32.516Z</t>
+    <t>2026-08-21T07:56:03.570Z</t>
   </si>
   <si>
     <t>Zero Critical / Zero High vulnerabilities detected (Overall Score: 72/100 Low Risk)</t>
@@ -1915,6 +1915,9 @@
     <t>Brute-Force Rate Limiting - Security Audit Check #3: Vulnerability analysis &amp; hardening verification</t>
   </si>
   <si>
+    <t>2026-08-21T07:56:03.571Z</t>
+  </si>
+  <si>
     <t>SEC-TC-0304</t>
   </si>
   <si>
@@ -2096,9 +2099,6 @@
   </si>
   <si>
     <t>REST API Request Schemas - Security Audit Check #13: Vulnerability analysis &amp; hardening verification</t>
-  </si>
-  <si>
-    <t>2026-08-10T08:42:32.517Z</t>
   </si>
   <si>
     <t>SEC-TC-0334</t>
@@ -3004,7 +3004,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
@@ -3030,7 +3030,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
@@ -3082,7 +3082,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>12</v>
@@ -3108,7 +3108,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>12</v>
@@ -3160,7 +3160,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
@@ -3212,7 +3212,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>12</v>
@@ -3238,7 +3238,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>12</v>
@@ -3264,7 +3264,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>12</v>
@@ -3342,7 +3342,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>12</v>
@@ -3368,7 +3368,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>12</v>
@@ -3420,7 +3420,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>12</v>
@@ -3446,7 +3446,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>12</v>
@@ -3472,7 +3472,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>12</v>
@@ -3498,7 +3498,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>12</v>
@@ -3576,7 +3576,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>12</v>
@@ -3628,7 +3628,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>12</v>
@@ -3680,7 +3680,7 @@
         <v>11</v>
       </c>
       <c r="E28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>12</v>
@@ -3732,7 +3732,7 @@
         <v>11</v>
       </c>
       <c r="E30" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>12</v>
@@ -3758,7 +3758,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>12</v>
@@ -3784,7 +3784,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>12</v>
@@ -3810,7 +3810,7 @@
         <v>11</v>
       </c>
       <c r="E33" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>12</v>
@@ -3836,7 +3836,7 @@
         <v>11</v>
       </c>
       <c r="E34" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>12</v>
@@ -3862,7 +3862,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>12</v>
@@ -3888,7 +3888,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>12</v>
@@ -3914,7 +3914,7 @@
         <v>11</v>
       </c>
       <c r="E37" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>12</v>
@@ -3940,7 +3940,7 @@
         <v>11</v>
       </c>
       <c r="E38" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>12</v>
@@ -3992,7 +3992,7 @@
         <v>11</v>
       </c>
       <c r="E40" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>12</v>
@@ -4018,7 +4018,7 @@
         <v>11</v>
       </c>
       <c r="E41" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>12</v>
@@ -4044,7 +4044,7 @@
         <v>11</v>
       </c>
       <c r="E42" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>12</v>
@@ -4096,7 +4096,7 @@
         <v>11</v>
       </c>
       <c r="E44" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>12</v>
@@ -4122,7 +4122,7 @@
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>12</v>
@@ -4148,7 +4148,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>12</v>
@@ -4174,7 +4174,7 @@
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>12</v>
@@ -4200,7 +4200,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>12</v>
@@ -4226,7 +4226,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>12</v>
@@ -4304,7 +4304,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
@@ -4330,7 +4330,7 @@
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>12</v>
@@ -4356,7 +4356,7 @@
         <v>11</v>
       </c>
       <c r="E54" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>12</v>
@@ -4382,7 +4382,7 @@
         <v>11</v>
       </c>
       <c r="E55" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>12</v>
@@ -4460,7 +4460,7 @@
         <v>11</v>
       </c>
       <c r="E58" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>12</v>
@@ -4486,7 +4486,7 @@
         <v>11</v>
       </c>
       <c r="E59" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>12</v>
@@ -4512,7 +4512,7 @@
         <v>11</v>
       </c>
       <c r="E60" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>12</v>
@@ -4538,7 +4538,7 @@
         <v>11</v>
       </c>
       <c r="E61" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>12</v>
@@ -4564,7 +4564,7 @@
         <v>11</v>
       </c>
       <c r="E62" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>12</v>
@@ -4590,7 +4590,7 @@
         <v>11</v>
       </c>
       <c r="E63" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>12</v>
@@ -4616,7 +4616,7 @@
         <v>11</v>
       </c>
       <c r="E64" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>12</v>
@@ -4642,7 +4642,7 @@
         <v>11</v>
       </c>
       <c r="E65" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>12</v>
@@ -4694,7 +4694,7 @@
         <v>11</v>
       </c>
       <c r="E67" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>12</v>
@@ -4746,7 +4746,7 @@
         <v>11</v>
       </c>
       <c r="E69" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>12</v>
@@ -4798,7 +4798,7 @@
         <v>11</v>
       </c>
       <c r="E71" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>12</v>
@@ -4824,7 +4824,7 @@
         <v>11</v>
       </c>
       <c r="E72" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>12</v>
@@ -4876,7 +4876,7 @@
         <v>11</v>
       </c>
       <c r="E74" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>12</v>
@@ -4928,7 +4928,7 @@
         <v>11</v>
       </c>
       <c r="E76" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>12</v>
@@ -4954,7 +4954,7 @@
         <v>11</v>
       </c>
       <c r="E77" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>12</v>
@@ -4980,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="E78" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>12</v>
@@ -5058,7 +5058,7 @@
         <v>11</v>
       </c>
       <c r="E81" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>12</v>
@@ -5084,7 +5084,7 @@
         <v>11</v>
       </c>
       <c r="E82" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>12</v>
@@ -5136,7 +5136,7 @@
         <v>11</v>
       </c>
       <c r="E84" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>12</v>
@@ -5162,7 +5162,7 @@
         <v>11</v>
       </c>
       <c r="E85" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>12</v>
@@ -5188,7 +5188,7 @@
         <v>11</v>
       </c>
       <c r="E86" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>12</v>
@@ -5214,7 +5214,7 @@
         <v>11</v>
       </c>
       <c r="E87" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>12</v>
@@ -5240,7 +5240,7 @@
         <v>11</v>
       </c>
       <c r="E88" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>12</v>
@@ -5266,7 +5266,7 @@
         <v>11</v>
       </c>
       <c r="E89" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>12</v>
@@ -5292,7 +5292,7 @@
         <v>11</v>
       </c>
       <c r="E90" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>12</v>
@@ -5370,7 +5370,7 @@
         <v>11</v>
       </c>
       <c r="E93" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>12</v>
@@ -5396,7 +5396,7 @@
         <v>11</v>
       </c>
       <c r="E94" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>12</v>
@@ -5422,7 +5422,7 @@
         <v>11</v>
       </c>
       <c r="E95" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>12</v>
@@ -5474,7 +5474,7 @@
         <v>11</v>
       </c>
       <c r="E97" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>12</v>
@@ -5552,7 +5552,7 @@
         <v>11</v>
       </c>
       <c r="E100" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>12</v>
@@ -5578,7 +5578,7 @@
         <v>11</v>
       </c>
       <c r="E101" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>12</v>
@@ -5604,7 +5604,7 @@
         <v>11</v>
       </c>
       <c r="E102" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>12</v>
@@ -5630,7 +5630,7 @@
         <v>11</v>
       </c>
       <c r="E103" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>12</v>
@@ -5656,7 +5656,7 @@
         <v>11</v>
       </c>
       <c r="E104" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>12</v>
@@ -5682,7 +5682,7 @@
         <v>11</v>
       </c>
       <c r="E105" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>12</v>
@@ -5734,7 +5734,7 @@
         <v>11</v>
       </c>
       <c r="E107" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>12</v>
@@ -5786,7 +5786,7 @@
         <v>11</v>
       </c>
       <c r="E109" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>12</v>
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="E110" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>12</v>
@@ -5838,7 +5838,7 @@
         <v>11</v>
       </c>
       <c r="E111" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>12</v>
@@ -5890,7 +5890,7 @@
         <v>11</v>
       </c>
       <c r="E113" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>12</v>
@@ -5942,7 +5942,7 @@
         <v>11</v>
       </c>
       <c r="E115" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>12</v>
@@ -5968,7 +5968,7 @@
         <v>11</v>
       </c>
       <c r="E116" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>12</v>
@@ -5994,7 +5994,7 @@
         <v>11</v>
       </c>
       <c r="E117" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>12</v>
@@ -6072,7 +6072,7 @@
         <v>11</v>
       </c>
       <c r="E120" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>12</v>
@@ -6124,7 +6124,7 @@
         <v>11</v>
       </c>
       <c r="E122" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>12</v>
@@ -6150,7 +6150,7 @@
         <v>11</v>
       </c>
       <c r="E123" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>12</v>
@@ -6176,7 +6176,7 @@
         <v>11</v>
       </c>
       <c r="E124" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>12</v>
@@ -6202,7 +6202,7 @@
         <v>11</v>
       </c>
       <c r="E125" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>12</v>
@@ -6228,7 +6228,7 @@
         <v>11</v>
       </c>
       <c r="E126" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>12</v>
@@ -6280,7 +6280,7 @@
         <v>11</v>
       </c>
       <c r="E128" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>12</v>
@@ -6306,7 +6306,7 @@
         <v>11</v>
       </c>
       <c r="E129" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>12</v>
@@ -6332,7 +6332,7 @@
         <v>11</v>
       </c>
       <c r="E130" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>12</v>
@@ -6358,7 +6358,7 @@
         <v>11</v>
       </c>
       <c r="E131" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>12</v>
@@ -6384,7 +6384,7 @@
         <v>11</v>
       </c>
       <c r="E132" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>12</v>
@@ -6410,7 +6410,7 @@
         <v>11</v>
       </c>
       <c r="E133" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>12</v>
@@ -6436,7 +6436,7 @@
         <v>11</v>
       </c>
       <c r="E134" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>12</v>
@@ -6462,7 +6462,7 @@
         <v>11</v>
       </c>
       <c r="E135" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>12</v>
@@ -6514,7 +6514,7 @@
         <v>11</v>
       </c>
       <c r="E137" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>12</v>
@@ -6540,7 +6540,7 @@
         <v>11</v>
       </c>
       <c r="E138" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>12</v>
@@ -6566,7 +6566,7 @@
         <v>11</v>
       </c>
       <c r="E139" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>12</v>
@@ -6618,7 +6618,7 @@
         <v>11</v>
       </c>
       <c r="E141" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>12</v>
@@ -6644,7 +6644,7 @@
         <v>11</v>
       </c>
       <c r="E142" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>12</v>
@@ -6670,7 +6670,7 @@
         <v>11</v>
       </c>
       <c r="E143" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>12</v>
@@ -6696,7 +6696,7 @@
         <v>11</v>
       </c>
       <c r="E144" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>12</v>
@@ -6722,7 +6722,7 @@
         <v>11</v>
       </c>
       <c r="E145" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>12</v>
@@ -6748,7 +6748,7 @@
         <v>11</v>
       </c>
       <c r="E146" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>12</v>
@@ -6774,7 +6774,7 @@
         <v>11</v>
       </c>
       <c r="E147" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>12</v>
@@ -6800,7 +6800,7 @@
         <v>11</v>
       </c>
       <c r="E148" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>12</v>
@@ -6826,7 +6826,7 @@
         <v>11</v>
       </c>
       <c r="E149" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>12</v>
@@ -6852,7 +6852,7 @@
         <v>11</v>
       </c>
       <c r="E150" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>12</v>
@@ -6878,7 +6878,7 @@
         <v>11</v>
       </c>
       <c r="E151" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>12</v>
@@ -6930,7 +6930,7 @@
         <v>11</v>
       </c>
       <c r="E153" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>12</v>
@@ -6956,7 +6956,7 @@
         <v>11</v>
       </c>
       <c r="E154" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>12</v>
@@ -6982,7 +6982,7 @@
         <v>11</v>
       </c>
       <c r="E155" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>12</v>
@@ -7034,7 +7034,7 @@
         <v>11</v>
       </c>
       <c r="E157" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>12</v>
@@ -7060,7 +7060,7 @@
         <v>11</v>
       </c>
       <c r="E158" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>12</v>
@@ -7112,7 +7112,7 @@
         <v>11</v>
       </c>
       <c r="E160" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>12</v>
@@ -7138,7 +7138,7 @@
         <v>11</v>
       </c>
       <c r="E161" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>12</v>
@@ -7216,7 +7216,7 @@
         <v>11</v>
       </c>
       <c r="E164" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>12</v>
@@ -7242,7 +7242,7 @@
         <v>11</v>
       </c>
       <c r="E165" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>12</v>
@@ -7268,7 +7268,7 @@
         <v>11</v>
       </c>
       <c r="E166" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>12</v>
@@ -7294,7 +7294,7 @@
         <v>11</v>
       </c>
       <c r="E167" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>12</v>
@@ -7320,7 +7320,7 @@
         <v>11</v>
       </c>
       <c r="E168" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>12</v>
@@ -7346,7 +7346,7 @@
         <v>11</v>
       </c>
       <c r="E169" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>12</v>
@@ -7398,7 +7398,7 @@
         <v>11</v>
       </c>
       <c r="E171" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>12</v>
@@ -7450,7 +7450,7 @@
         <v>11</v>
       </c>
       <c r="E173" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>12</v>
@@ -7476,7 +7476,7 @@
         <v>11</v>
       </c>
       <c r="E174" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>12</v>
@@ -7502,7 +7502,7 @@
         <v>11</v>
       </c>
       <c r="E175" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>12</v>
@@ -7528,7 +7528,7 @@
         <v>11</v>
       </c>
       <c r="E176" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>12</v>
@@ -7554,7 +7554,7 @@
         <v>11</v>
       </c>
       <c r="E177" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>12</v>
@@ -7580,7 +7580,7 @@
         <v>11</v>
       </c>
       <c r="E178" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>12</v>
@@ -7606,7 +7606,7 @@
         <v>11</v>
       </c>
       <c r="E179" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>12</v>
@@ -7632,7 +7632,7 @@
         <v>11</v>
       </c>
       <c r="E180" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>12</v>
@@ -7684,7 +7684,7 @@
         <v>11</v>
       </c>
       <c r="E182" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>12</v>
@@ -7710,7 +7710,7 @@
         <v>11</v>
       </c>
       <c r="E183" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>12</v>
@@ -7736,7 +7736,7 @@
         <v>11</v>
       </c>
       <c r="E184" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>12</v>
@@ -7788,7 +7788,7 @@
         <v>11</v>
       </c>
       <c r="E186" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>12</v>
@@ -7840,7 +7840,7 @@
         <v>11</v>
       </c>
       <c r="E188" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>12</v>
@@ -7866,7 +7866,7 @@
         <v>11</v>
       </c>
       <c r="E189" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>12</v>
@@ -7892,7 +7892,7 @@
         <v>11</v>
       </c>
       <c r="E190" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>12</v>
@@ -7918,7 +7918,7 @@
         <v>11</v>
       </c>
       <c r="E191" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>12</v>
@@ -7944,7 +7944,7 @@
         <v>11</v>
       </c>
       <c r="E192" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>12</v>
@@ -7970,7 +7970,7 @@
         <v>11</v>
       </c>
       <c r="E193" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>12</v>
@@ -7996,7 +7996,7 @@
         <v>11</v>
       </c>
       <c r="E194" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>12</v>
@@ -8022,7 +8022,7 @@
         <v>11</v>
       </c>
       <c r="E195" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>12</v>
@@ -8048,7 +8048,7 @@
         <v>11</v>
       </c>
       <c r="E196" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>12</v>
@@ -8074,7 +8074,7 @@
         <v>11</v>
       </c>
       <c r="E197" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>12</v>
@@ -8100,7 +8100,7 @@
         <v>11</v>
       </c>
       <c r="E198" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>12</v>
@@ -8126,7 +8126,7 @@
         <v>11</v>
       </c>
       <c r="E199" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>12</v>
@@ -8178,7 +8178,7 @@
         <v>11</v>
       </c>
       <c r="E201" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>12</v>
@@ -8204,7 +8204,7 @@
         <v>11</v>
       </c>
       <c r="E202" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>12</v>
@@ -8256,7 +8256,7 @@
         <v>11</v>
       </c>
       <c r="E204" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>12</v>
@@ -8282,7 +8282,7 @@
         <v>11</v>
       </c>
       <c r="E205" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>12</v>
@@ -8308,7 +8308,7 @@
         <v>11</v>
       </c>
       <c r="E206" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>12</v>
@@ -8334,7 +8334,7 @@
         <v>11</v>
       </c>
       <c r="E207" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>12</v>
@@ -8360,7 +8360,7 @@
         <v>11</v>
       </c>
       <c r="E208" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>12</v>
@@ -8386,7 +8386,7 @@
         <v>11</v>
       </c>
       <c r="E209" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>12</v>
@@ -8412,7 +8412,7 @@
         <v>11</v>
       </c>
       <c r="E210" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>12</v>
@@ -8438,7 +8438,7 @@
         <v>11</v>
       </c>
       <c r="E211" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>12</v>
@@ -8464,7 +8464,7 @@
         <v>11</v>
       </c>
       <c r="E212" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>12</v>
@@ -8490,7 +8490,7 @@
         <v>11</v>
       </c>
       <c r="E213" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>12</v>
@@ -8542,7 +8542,7 @@
         <v>11</v>
       </c>
       <c r="E215" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>12</v>
@@ -8594,7 +8594,7 @@
         <v>11</v>
       </c>
       <c r="E217" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>12</v>
@@ -8620,7 +8620,7 @@
         <v>11</v>
       </c>
       <c r="E218" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>12</v>
@@ -8646,7 +8646,7 @@
         <v>11</v>
       </c>
       <c r="E219" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>12</v>
@@ -8672,7 +8672,7 @@
         <v>11</v>
       </c>
       <c r="E220" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>12</v>
@@ -8698,7 +8698,7 @@
         <v>11</v>
       </c>
       <c r="E221" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>12</v>
@@ -8724,7 +8724,7 @@
         <v>11</v>
       </c>
       <c r="E222" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>12</v>
@@ -8750,7 +8750,7 @@
         <v>11</v>
       </c>
       <c r="E223" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>12</v>
@@ -8776,7 +8776,7 @@
         <v>11</v>
       </c>
       <c r="E224" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>12</v>
@@ -8802,7 +8802,7 @@
         <v>11</v>
       </c>
       <c r="E225" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>12</v>
@@ -8828,7 +8828,7 @@
         <v>11</v>
       </c>
       <c r="E226" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>12</v>
@@ -8854,7 +8854,7 @@
         <v>11</v>
       </c>
       <c r="E227" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>12</v>
@@ -8932,7 +8932,7 @@
         <v>11</v>
       </c>
       <c r="E230" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>12</v>
@@ -8958,7 +8958,7 @@
         <v>11</v>
       </c>
       <c r="E231" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>12</v>
@@ -9010,7 +9010,7 @@
         <v>11</v>
       </c>
       <c r="E233" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>12</v>
@@ -9036,7 +9036,7 @@
         <v>11</v>
       </c>
       <c r="E234" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
@@ -9062,7 +9062,7 @@
         <v>11</v>
       </c>
       <c r="E235" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>12</v>
@@ -9088,7 +9088,7 @@
         <v>11</v>
       </c>
       <c r="E236" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
@@ -9114,7 +9114,7 @@
         <v>11</v>
       </c>
       <c r="E237" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
@@ -9140,7 +9140,7 @@
         <v>11</v>
       </c>
       <c r="E238" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
@@ -9166,7 +9166,7 @@
         <v>11</v>
       </c>
       <c r="E239" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
@@ -9244,7 +9244,7 @@
         <v>11</v>
       </c>
       <c r="E242" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>12</v>
@@ -9296,7 +9296,7 @@
         <v>11</v>
       </c>
       <c r="E244" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
@@ -9322,7 +9322,7 @@
         <v>11</v>
       </c>
       <c r="E245" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
@@ -9348,7 +9348,7 @@
         <v>11</v>
       </c>
       <c r="E246" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
@@ -9374,7 +9374,7 @@
         <v>11</v>
       </c>
       <c r="E247" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>12</v>
@@ -9400,7 +9400,7 @@
         <v>11</v>
       </c>
       <c r="E248" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
@@ -9452,7 +9452,7 @@
         <v>11</v>
       </c>
       <c r="E250" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>12</v>
@@ -9478,7 +9478,7 @@
         <v>11</v>
       </c>
       <c r="E251" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
@@ -9504,7 +9504,7 @@
         <v>11</v>
       </c>
       <c r="E252" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
@@ -9530,7 +9530,7 @@
         <v>11</v>
       </c>
       <c r="E253" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>12</v>
@@ -9582,7 +9582,7 @@
         <v>11</v>
       </c>
       <c r="E255" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
@@ -9608,7 +9608,7 @@
         <v>11</v>
       </c>
       <c r="E256" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>12</v>
@@ -9634,7 +9634,7 @@
         <v>11</v>
       </c>
       <c r="E257" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>12</v>
@@ -9686,7 +9686,7 @@
         <v>11</v>
       </c>
       <c r="E259" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>12</v>
@@ -9712,7 +9712,7 @@
         <v>11</v>
       </c>
       <c r="E260" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>12</v>
@@ -9738,7 +9738,7 @@
         <v>11</v>
       </c>
       <c r="E261" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>12</v>
@@ -9764,7 +9764,7 @@
         <v>11</v>
       </c>
       <c r="E262" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>12</v>
@@ -9790,7 +9790,7 @@
         <v>11</v>
       </c>
       <c r="E263" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>12</v>
@@ -9816,7 +9816,7 @@
         <v>11</v>
       </c>
       <c r="E264" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>12</v>
@@ -9842,7 +9842,7 @@
         <v>11</v>
       </c>
       <c r="E265" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>12</v>
@@ -9868,7 +9868,7 @@
         <v>11</v>
       </c>
       <c r="E266" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>12</v>
@@ -9894,7 +9894,7 @@
         <v>11</v>
       </c>
       <c r="E267" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>12</v>
@@ -9920,7 +9920,7 @@
         <v>11</v>
       </c>
       <c r="E268" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>12</v>
@@ -9946,7 +9946,7 @@
         <v>11</v>
       </c>
       <c r="E269" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>12</v>
@@ -9972,7 +9972,7 @@
         <v>11</v>
       </c>
       <c r="E270" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>12</v>
@@ -9998,7 +9998,7 @@
         <v>11</v>
       </c>
       <c r="E271" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>12</v>
@@ -10024,7 +10024,7 @@
         <v>11</v>
       </c>
       <c r="E272" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>12</v>
@@ -10050,7 +10050,7 @@
         <v>11</v>
       </c>
       <c r="E273" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>12</v>
@@ -10076,7 +10076,7 @@
         <v>11</v>
       </c>
       <c r="E274" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>12</v>
@@ -10154,7 +10154,7 @@
         <v>11</v>
       </c>
       <c r="E277" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>12</v>
@@ -10180,7 +10180,7 @@
         <v>11</v>
       </c>
       <c r="E278" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
@@ -10232,7 +10232,7 @@
         <v>11</v>
       </c>
       <c r="E280" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
@@ -10258,7 +10258,7 @@
         <v>11</v>
       </c>
       <c r="E281" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>12</v>
@@ -10284,7 +10284,7 @@
         <v>11</v>
       </c>
       <c r="E282" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>12</v>
@@ -10310,7 +10310,7 @@
         <v>11</v>
       </c>
       <c r="E283" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>12</v>
@@ -10336,7 +10336,7 @@
         <v>11</v>
       </c>
       <c r="E284" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>12</v>
@@ -10362,7 +10362,7 @@
         <v>11</v>
       </c>
       <c r="E285" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
@@ -10388,7 +10388,7 @@
         <v>11</v>
       </c>
       <c r="E286" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
@@ -10440,7 +10440,7 @@
         <v>11</v>
       </c>
       <c r="E288" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>12</v>
@@ -10466,7 +10466,7 @@
         <v>11</v>
       </c>
       <c r="E289" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>12</v>
@@ -10518,7 +10518,7 @@
         <v>11</v>
       </c>
       <c r="E291" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>12</v>
@@ -10544,7 +10544,7 @@
         <v>11</v>
       </c>
       <c r="E292" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>12</v>
@@ -10596,7 +10596,7 @@
         <v>11</v>
       </c>
       <c r="E294" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>12</v>
@@ -10622,7 +10622,7 @@
         <v>11</v>
       </c>
       <c r="E295" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>12</v>
@@ -10648,7 +10648,7 @@
         <v>11</v>
       </c>
       <c r="E296" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>12</v>
@@ -10700,7 +10700,7 @@
         <v>11</v>
       </c>
       <c r="E298" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>12</v>
@@ -10752,7 +10752,7 @@
         <v>11</v>
       </c>
       <c r="E300" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
@@ -10778,7 +10778,7 @@
         <v>11</v>
       </c>
       <c r="E301" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>12</v>
@@ -10804,7 +10804,7 @@
         <v>11</v>
       </c>
       <c r="E302" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
@@ -10830,7 +10830,7 @@
         <v>11</v>
       </c>
       <c r="E303" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
@@ -10856,13 +10856,13 @@
         <v>11</v>
       </c>
       <c r="E304" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>14</v>
@@ -10870,25 +10870,25 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B305" s="4" t="s">
         <v>628</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E305" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H305" s="4" t="s">
         <v>14</v>
@@ -10896,25 +10896,25 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E306" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>14</v>
@@ -10922,25 +10922,25 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B307" s="4" t="s">
         <v>628</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E307" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H307" s="4" t="s">
         <v>14</v>
@@ -10948,25 +10948,25 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E308" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>14</v>
@@ -10974,25 +10974,25 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B309" s="4" t="s">
         <v>628</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E309" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H309" s="4" t="s">
         <v>14</v>
@@ -11000,25 +11000,25 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E310" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>14</v>
@@ -11026,25 +11026,25 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B311" s="4" t="s">
         <v>628</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E311" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H311" s="4" t="s">
         <v>14</v>
@@ -11052,25 +11052,25 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E312" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>14</v>
@@ -11078,25 +11078,25 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B313" s="4" t="s">
         <v>628</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E313" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G313" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H313" s="4" t="s">
         <v>14</v>
@@ -11104,13 +11104,13 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>11</v>
@@ -11122,7 +11122,7 @@
         <v>12</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>14</v>
@@ -11130,25 +11130,25 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B315" s="4" t="s">
         <v>628</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E315" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G315" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H315" s="4" t="s">
         <v>14</v>
@@ -11156,13 +11156,13 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>11</v>
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>14</v>
@@ -11182,25 +11182,25 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B317" s="4" t="s">
         <v>628</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E317" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H317" s="4" t="s">
         <v>14</v>
@@ -11208,25 +11208,25 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E318" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>14</v>
@@ -11234,25 +11234,25 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B319" s="4" t="s">
         <v>628</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E319" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H319" s="4" t="s">
         <v>14</v>
@@ -11260,13 +11260,13 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>628</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>11</v>
@@ -11278,7 +11278,7 @@
         <v>12</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>14</v>
@@ -11286,25 +11286,25 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B321" s="4" t="s">
         <v>628</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E321" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H321" s="4" t="s">
         <v>14</v>
@@ -11312,25 +11312,25 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E322" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>14</v>
@@ -11338,25 +11338,25 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E323" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H323" s="4" t="s">
         <v>14</v>
@@ -11364,25 +11364,25 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E324" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>14</v>
@@ -11390,25 +11390,25 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E325" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H325" s="4" t="s">
         <v>14</v>
@@ -11416,25 +11416,25 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D326" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E326" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>14</v>
@@ -11442,25 +11442,25 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E327" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G327" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H327" s="4" t="s">
         <v>14</v>
@@ -11468,25 +11468,25 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E328" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>14</v>
@@ -11494,25 +11494,25 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E329" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H329" s="4" t="s">
         <v>14</v>
@@ -11520,25 +11520,25 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E330" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>14</v>
@@ -11546,25 +11546,25 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>11</v>
       </c>
       <c r="E331" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H331" s="4" t="s">
         <v>14</v>
@@ -11572,25 +11572,25 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E332" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>14</v>
@@ -11598,13 +11598,13 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>11</v>
@@ -11616,7 +11616,7 @@
         <v>12</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>13</v>
+        <v>634</v>
       </c>
       <c r="H333" s="4" t="s">
         <v>14</v>
@@ -11624,25 +11624,25 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E334" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>14</v>
@@ -11653,7 +11653,7 @@
         <v>696</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>697</v>
@@ -11662,13 +11662,13 @@
         <v>11</v>
       </c>
       <c r="E335" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H335" s="4" t="s">
         <v>14</v>
@@ -11679,7 +11679,7 @@
         <v>698</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>699</v>
@@ -11688,13 +11688,13 @@
         <v>11</v>
       </c>
       <c r="E336" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>14</v>
@@ -11705,7 +11705,7 @@
         <v>700</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>701</v>
@@ -11714,13 +11714,13 @@
         <v>11</v>
       </c>
       <c r="E337" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G337" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H337" s="4" t="s">
         <v>14</v>
@@ -11731,7 +11731,7 @@
         <v>702</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>703</v>
@@ -11740,13 +11740,13 @@
         <v>11</v>
       </c>
       <c r="E338" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>14</v>
@@ -11757,7 +11757,7 @@
         <v>704</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>705</v>
@@ -11766,13 +11766,13 @@
         <v>11</v>
       </c>
       <c r="E339" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>14</v>
@@ -11783,7 +11783,7 @@
         <v>706</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>707</v>
@@ -11792,13 +11792,13 @@
         <v>11</v>
       </c>
       <c r="E340" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H340" s="2" t="s">
         <v>14</v>
@@ -11809,7 +11809,7 @@
         <v>708</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>709</v>
@@ -11824,7 +11824,7 @@
         <v>12</v>
       </c>
       <c r="G341" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H341" s="4" t="s">
         <v>14</v>
@@ -11844,13 +11844,13 @@
         <v>11</v>
       </c>
       <c r="E342" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H342" s="2" t="s">
         <v>14</v>
@@ -11870,13 +11870,13 @@
         <v>11</v>
       </c>
       <c r="E343" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G343" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H343" s="4" t="s">
         <v>14</v>
@@ -11896,13 +11896,13 @@
         <v>11</v>
       </c>
       <c r="E344" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H344" s="2" t="s">
         <v>14</v>
@@ -11922,13 +11922,13 @@
         <v>11</v>
       </c>
       <c r="E345" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G345" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H345" s="4" t="s">
         <v>14</v>
@@ -11954,7 +11954,7 @@
         <v>12</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H346" s="2" t="s">
         <v>14</v>
@@ -11974,13 +11974,13 @@
         <v>11</v>
       </c>
       <c r="E347" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H347" s="4" t="s">
         <v>14</v>
@@ -12000,13 +12000,13 @@
         <v>11</v>
       </c>
       <c r="E348" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H348" s="2" t="s">
         <v>14</v>
@@ -12026,13 +12026,13 @@
         <v>11</v>
       </c>
       <c r="E349" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H349" s="4" t="s">
         <v>14</v>
@@ -12052,13 +12052,13 @@
         <v>11</v>
       </c>
       <c r="E350" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H350" s="2" t="s">
         <v>14</v>
@@ -12078,13 +12078,13 @@
         <v>11</v>
       </c>
       <c r="E351" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G351" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H351" s="4" t="s">
         <v>14</v>
@@ -12104,13 +12104,13 @@
         <v>11</v>
       </c>
       <c r="E352" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H352" s="2" t="s">
         <v>14</v>
@@ -12130,13 +12130,13 @@
         <v>11</v>
       </c>
       <c r="E353" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H353" s="4" t="s">
         <v>14</v>
@@ -12156,13 +12156,13 @@
         <v>11</v>
       </c>
       <c r="E354" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H354" s="2" t="s">
         <v>14</v>
@@ -12182,13 +12182,13 @@
         <v>11</v>
       </c>
       <c r="E355" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H355" s="4" t="s">
         <v>14</v>
@@ -12208,13 +12208,13 @@
         <v>11</v>
       </c>
       <c r="E356" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H356" s="2" t="s">
         <v>14</v>
@@ -12234,13 +12234,13 @@
         <v>11</v>
       </c>
       <c r="E357" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G357" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H357" s="4" t="s">
         <v>14</v>
@@ -12260,13 +12260,13 @@
         <v>11</v>
       </c>
       <c r="E358" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H358" s="2" t="s">
         <v>14</v>
@@ -12286,13 +12286,13 @@
         <v>11</v>
       </c>
       <c r="E359" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G359" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H359" s="4" t="s">
         <v>14</v>
@@ -12312,13 +12312,13 @@
         <v>11</v>
       </c>
       <c r="E360" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H360" s="2" t="s">
         <v>14</v>
@@ -12338,13 +12338,13 @@
         <v>11</v>
       </c>
       <c r="E361" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G361" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H361" s="4" t="s">
         <v>14</v>
@@ -12364,13 +12364,13 @@
         <v>11</v>
       </c>
       <c r="E362" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H362" s="2" t="s">
         <v>14</v>
@@ -12390,13 +12390,13 @@
         <v>11</v>
       </c>
       <c r="E363" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G363" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H363" s="4" t="s">
         <v>14</v>
@@ -12416,13 +12416,13 @@
         <v>11</v>
       </c>
       <c r="E364" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H364" s="2" t="s">
         <v>14</v>
@@ -12442,13 +12442,13 @@
         <v>11</v>
       </c>
       <c r="E365" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H365" s="4" t="s">
         <v>14</v>
@@ -12468,13 +12468,13 @@
         <v>11</v>
       </c>
       <c r="E366" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H366" s="2" t="s">
         <v>14</v>
@@ -12494,13 +12494,13 @@
         <v>11</v>
       </c>
       <c r="E367" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H367" s="4" t="s">
         <v>14</v>
@@ -12520,13 +12520,13 @@
         <v>11</v>
       </c>
       <c r="E368" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H368" s="2" t="s">
         <v>14</v>
@@ -12546,13 +12546,13 @@
         <v>11</v>
       </c>
       <c r="E369" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H369" s="4" t="s">
         <v>14</v>
@@ -12572,13 +12572,13 @@
         <v>11</v>
       </c>
       <c r="E370" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H370" s="2" t="s">
         <v>14</v>
@@ -12598,13 +12598,13 @@
         <v>11</v>
       </c>
       <c r="E371" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>14</v>
@@ -12630,7 +12630,7 @@
         <v>12</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H372" s="2" t="s">
         <v>14</v>
@@ -12650,13 +12650,13 @@
         <v>11</v>
       </c>
       <c r="E373" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H373" s="4" t="s">
         <v>14</v>
@@ -12676,13 +12676,13 @@
         <v>11</v>
       </c>
       <c r="E374" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H374" s="2" t="s">
         <v>14</v>
@@ -12702,13 +12702,13 @@
         <v>11</v>
       </c>
       <c r="E375" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H375" s="4" t="s">
         <v>14</v>
@@ -12728,13 +12728,13 @@
         <v>11</v>
       </c>
       <c r="E376" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H376" s="2" t="s">
         <v>14</v>
@@ -12760,7 +12760,7 @@
         <v>12</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H377" s="4" t="s">
         <v>14</v>
@@ -12780,13 +12780,13 @@
         <v>11</v>
       </c>
       <c r="E378" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H378" s="2" t="s">
         <v>14</v>
@@ -12812,7 +12812,7 @@
         <v>12</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H379" s="4" t="s">
         <v>14</v>
@@ -12832,13 +12832,13 @@
         <v>11</v>
       </c>
       <c r="E380" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H380" s="2" t="s">
         <v>14</v>
@@ -12858,13 +12858,13 @@
         <v>11</v>
       </c>
       <c r="E381" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G381" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H381" s="4" t="s">
         <v>14</v>
@@ -12884,13 +12884,13 @@
         <v>11</v>
       </c>
       <c r="E382" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H382" s="2" t="s">
         <v>14</v>
@@ -12910,13 +12910,13 @@
         <v>11</v>
       </c>
       <c r="E383" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H383" s="4" t="s">
         <v>14</v>
@@ -12936,13 +12936,13 @@
         <v>11</v>
       </c>
       <c r="E384" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H384" s="2" t="s">
         <v>14</v>
@@ -12962,13 +12962,13 @@
         <v>11</v>
       </c>
       <c r="E385" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G385" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H385" s="4" t="s">
         <v>14</v>
@@ -12994,7 +12994,7 @@
         <v>12</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H386" s="2" t="s">
         <v>14</v>
@@ -13014,13 +13014,13 @@
         <v>11</v>
       </c>
       <c r="E387" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G387" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H387" s="4" t="s">
         <v>14</v>
@@ -13040,13 +13040,13 @@
         <v>11</v>
       </c>
       <c r="E388" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H388" s="2" t="s">
         <v>14</v>
@@ -13066,13 +13066,13 @@
         <v>11</v>
       </c>
       <c r="E389" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H389" s="4" t="s">
         <v>14</v>
@@ -13092,13 +13092,13 @@
         <v>11</v>
       </c>
       <c r="E390" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H390" s="2" t="s">
         <v>14</v>
@@ -13124,7 +13124,7 @@
         <v>12</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H391" s="4" t="s">
         <v>14</v>
@@ -13144,13 +13144,13 @@
         <v>11</v>
       </c>
       <c r="E392" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H392" s="2" t="s">
         <v>14</v>
@@ -13170,13 +13170,13 @@
         <v>11</v>
       </c>
       <c r="E393" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H393" s="4" t="s">
         <v>14</v>
@@ -13202,7 +13202,7 @@
         <v>12</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H394" s="2" t="s">
         <v>14</v>
@@ -13222,13 +13222,13 @@
         <v>11</v>
       </c>
       <c r="E395" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H395" s="4" t="s">
         <v>14</v>
@@ -13248,13 +13248,13 @@
         <v>11</v>
       </c>
       <c r="E396" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H396" s="2" t="s">
         <v>14</v>
@@ -13274,13 +13274,13 @@
         <v>11</v>
       </c>
       <c r="E397" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G397" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H397" s="4" t="s">
         <v>14</v>
@@ -13306,7 +13306,7 @@
         <v>12</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H398" s="2" t="s">
         <v>14</v>
@@ -13326,13 +13326,13 @@
         <v>11</v>
       </c>
       <c r="E399" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H399" s="4" t="s">
         <v>14</v>
@@ -13352,13 +13352,13 @@
         <v>11</v>
       </c>
       <c r="E400" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H400" s="2" t="s">
         <v>14</v>
@@ -13378,13 +13378,13 @@
         <v>11</v>
       </c>
       <c r="E401" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G401" s="4" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="H401" s="4" t="s">
         <v>14</v>
